--- a/Mangrove_Test.xlsx
+++ b/Mangrove_Test.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c33f6df449a52773/Documents/EVE/EVE-valuation-engine/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="59" documentId="11_7E652DE828F45CA725D9AAB52C5BDA16E64B0D51" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7CDEA379-6AC9-4D70-BFA5-04EA26DB83D1}"/>
+  <xr:revisionPtr revIDLastSave="74" documentId="11_7E652DE828F45CA725D9AAB52C5BDA16E64B0D51" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B1296708-31A8-486C-BEE9-BE98E05C3951}"/>
   <bookViews>
-    <workbookView xWindow="-16320" yWindow="-5340" windowWidth="16440" windowHeight="28320" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Mangrove Calculator" sheetId="1" r:id="rId1"/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="72">
   <si>
     <t>EVE Mangrove Ecosystem Services — Test Calculator</t>
   </si>
@@ -91,9 +91,6 @@
     <t>× Area</t>
   </si>
   <si>
-    <t>× Intactness</t>
-  </si>
-  <si>
     <t>× Regional</t>
   </si>
   <si>
@@ -269,6 +266,12 @@
   </si>
   <si>
     <t>M4 answer</t>
+  </si>
+  <si>
+    <t>Final</t>
+  </si>
+  <si>
+    <t>HD/BBI</t>
   </si>
 </sst>
 </file>
@@ -792,7 +795,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K40"/>
+  <dimension ref="A1:L40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" customWidth="1"/>
@@ -800,11 +803,11 @@
     <col min="3" max="3" width="24" customWidth="1"/>
     <col min="4" max="4" width="11" customWidth="1"/>
     <col min="5" max="9" width="13" customWidth="1"/>
-    <col min="10" max="10" width="12" customWidth="1"/>
-    <col min="11" max="11" width="22" customWidth="1"/>
+    <col min="10" max="11" width="12" customWidth="1"/>
+    <col min="12" max="12" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
@@ -818,8 +821,9 @@
       <c r="I1" s="23"/>
       <c r="J1" s="23"/>
       <c r="K1" s="23"/>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L1" s="23"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="26" t="s">
         <v>1</v>
       </c>
@@ -833,8 +837,9 @@
       <c r="I3" s="23"/>
       <c r="J3" s="23"/>
       <c r="K3" s="23"/>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L3" s="23"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -842,7 +847,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -850,7 +855,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -858,7 +863,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -869,7 +874,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>7</v>
       </c>
@@ -883,33 +888,36 @@
         <v>10</v>
       </c>
       <c r="E9" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="I9" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="J9" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="F9" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="H9" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="I9" s="5" t="s">
+      <c r="K9" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="J9" s="5" t="s">
+      <c r="L9" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="K9" s="5" t="s">
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" s="6" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="s">
+      <c r="B10" s="6" t="s">
         <v>14</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>15</v>
       </c>
       <c r="C10" s="7">
         <v>117</v>
@@ -927,30 +935,33 @@
         <v>0.5</v>
       </c>
       <c r="G10" s="8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="H10" s="8" cm="1">
         <f t="array" ref="H10">_xlfn.SWITCH(HLOOKUP(A10, 'Indicator Mapping'!$A$4:$W$12, 5, FALSE), "P", 1, "S", 0.5, 0)</f>
         <v>0.5</v>
       </c>
       <c r="I10" s="8">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J10" s="8">
-        <f t="shared" ref="J10:J31" si="2">$B$6</f>
-        <v>1</v>
-      </c>
-      <c r="K10" s="9">
-        <f>C10*$B$4*$B$5*$B$6*F10*G10*H10*I10</f>
-        <v>29250</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+        <v>0.51</v>
+      </c>
+      <c r="K10" s="8">
+        <f>(((G10*F10)+(H10*I10))/1)*J10*E10</f>
+        <v>0.255</v>
+      </c>
+      <c r="L10" s="9">
+        <f>C10*D10*K10</f>
+        <v>29835</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C11" s="7">
         <v>6070</v>
@@ -978,20 +989,24 @@
         <v>1</v>
       </c>
       <c r="J11" s="8">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="K11" s="9">
-        <f t="shared" ref="K11:K31" si="3">C11*$B$4*$B$5*$B$6*F11*G11*H11*I11</f>
-        <v>3035000</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+        <f t="shared" ref="J10:J31" si="2">$B$6</f>
+        <v>1</v>
+      </c>
+      <c r="K11" s="8">
+        <f t="shared" ref="K11:K31" si="3">((G11*F11)+(H11*I11))/1</f>
+        <v>1.5</v>
+      </c>
+      <c r="L11" s="9">
+        <f t="shared" ref="L11:L31" si="4">C11*D11*$B$4*$B$5*$B$6*F11*G11*H11*I11</f>
+        <v>3035000000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C12" s="7">
         <v>15</v>
@@ -1022,17 +1037,21 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="K12" s="9">
+      <c r="K12" s="8">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="L12" s="9">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C13" s="7">
         <v>4</v>
@@ -1063,17 +1082,21 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="K13" s="9">
+      <c r="K13" s="8">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L13" s="9">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C14" s="7">
         <v>299</v>
@@ -1104,17 +1127,21 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="K14" s="9">
+      <c r="K14" s="8">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L14" s="9">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C15" s="7">
         <v>0</v>
@@ -1145,17 +1172,21 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="K15" s="9">
+      <c r="K15" s="8">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L15" s="9">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16" s="6" t="s">
         <v>21</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>22</v>
       </c>
       <c r="C16" s="7">
         <v>705</v>
@@ -1186,17 +1217,21 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="K16" s="9">
+      <c r="K16" s="8">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="L16" s="9">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C17" s="7">
         <v>3417</v>
@@ -1227,17 +1262,21 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="K17" s="9">
+      <c r="K17" s="8">
         <f t="shared" si="3"/>
-        <v>1708500</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+        <v>1.5</v>
+      </c>
+      <c r="L17" s="9">
+        <f t="shared" si="4"/>
+        <v>1708500000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C18" s="7">
         <v>5384</v>
@@ -1268,17 +1307,21 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="K18" s="9">
+      <c r="K18" s="8">
         <f t="shared" si="3"/>
-        <v>5384000</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="L18" s="9">
+        <f t="shared" si="4"/>
+        <v>5384000000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C19" s="7">
         <v>0</v>
@@ -1309,17 +1352,21 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="K19" s="9">
+      <c r="K19" s="8">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="L19" s="9">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C20" s="7">
         <v>7119</v>
@@ -1350,17 +1397,21 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="K20" s="9">
+      <c r="K20" s="8">
         <f t="shared" si="3"/>
-        <v>3559500</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+        <v>1.5</v>
+      </c>
+      <c r="L20" s="9">
+        <f t="shared" si="4"/>
+        <v>3559500000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C21" s="7">
         <v>1005</v>
@@ -1391,17 +1442,21 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="K21" s="9">
+      <c r="K21" s="8">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="L21" s="9">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C22" s="7">
         <v>670</v>
@@ -1432,17 +1487,21 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="K22" s="9">
+      <c r="K22" s="8">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L22" s="9">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C23" s="7">
         <v>0</v>
@@ -1473,17 +1532,21 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="K23" s="9">
+      <c r="K23" s="8">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L23" s="9">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C24" s="7">
         <v>0</v>
@@ -1514,17 +1577,21 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="K24" s="9">
+      <c r="K24" s="8">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L24" s="9">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B25" s="6" t="s">
         <v>31</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>32</v>
       </c>
       <c r="C25" s="7">
         <v>743</v>
@@ -1555,17 +1622,21 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="K25" s="9">
+      <c r="K25" s="8">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L25" s="9">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C26" s="7">
         <v>3190</v>
@@ -1596,17 +1667,21 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="K26" s="9">
+      <c r="K26" s="8">
         <f t="shared" si="3"/>
-        <v>3190000</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+        <v>2</v>
+      </c>
+      <c r="L26" s="9">
+        <f t="shared" si="4"/>
+        <v>3190000000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B27" s="6" t="s">
         <v>34</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>35</v>
       </c>
       <c r="C27" s="7">
         <v>0</v>
@@ -1637,17 +1712,21 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="K27" s="9">
+      <c r="K27" s="8">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="L27" s="9">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C28" s="7">
         <v>2173</v>
@@ -1678,17 +1757,21 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="K28" s="9">
+      <c r="K28" s="8">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+        <v>0.5</v>
+      </c>
+      <c r="L28" s="9">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C29" s="7">
         <v>0</v>
@@ -1719,17 +1802,21 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="K29" s="9">
+      <c r="K29" s="8">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L29" s="9">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C30" s="7">
         <v>0</v>
@@ -1760,17 +1847,21 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="K30" s="9">
+      <c r="K30" s="8">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L30" s="9">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C31" s="7">
         <v>0</v>
@@ -1801,14 +1892,18 @@
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="K31" s="9">
+      <c r="K31" s="8">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="L31" s="9">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" s="27" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B32" s="23"/>
       <c r="C32" s="23"/>
@@ -1819,14 +1914,14 @@
       <c r="H32" s="23"/>
       <c r="I32" s="23"/>
       <c r="J32" s="23"/>
-      <c r="K32" s="10">
-        <f>SUM(K10:K31)</f>
-        <v>16906250</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L32" s="10">
+        <f>SUM(L10:L31)</f>
+        <v>16877029835</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" s="22" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B33" s="23"/>
       <c r="C33" s="23"/>
@@ -1837,14 +1932,14 @@
       <c r="H33" s="23"/>
       <c r="I33" s="23"/>
       <c r="J33" s="23"/>
-      <c r="K33" s="11">
-        <f>K32/$B$4</f>
-        <v>16906.25</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L33" s="11">
+        <f>L32/$B$4</f>
+        <v>16877029.835000001</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" s="28" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B35" s="23"/>
       <c r="C35" s="23"/>
@@ -1856,10 +1951,11 @@
       <c r="I35" s="23"/>
       <c r="J35" s="23"/>
       <c r="K35" s="23"/>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L35" s="23"/>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" s="24" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B36" s="23"/>
       <c r="C36" s="23"/>
@@ -1871,10 +1967,11 @@
       <c r="I36" s="23"/>
       <c r="J36" s="23"/>
       <c r="K36" s="23"/>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L36" s="23"/>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" s="24" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B37" s="23"/>
       <c r="C37" s="23"/>
@@ -1886,10 +1983,11 @@
       <c r="I37" s="23"/>
       <c r="J37" s="23"/>
       <c r="K37" s="23"/>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L37" s="23"/>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" s="24" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B38" s="23"/>
       <c r="C38" s="23"/>
@@ -1901,10 +1999,11 @@
       <c r="I38" s="23"/>
       <c r="J38" s="23"/>
       <c r="K38" s="23"/>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L38" s="23"/>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" s="24" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B39" s="23"/>
       <c r="C39" s="23"/>
@@ -1916,10 +2015,11 @@
       <c r="I39" s="23"/>
       <c r="J39" s="23"/>
       <c r="K39" s="23"/>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L39" s="23"/>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" s="24" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B40" s="23"/>
       <c r="C40" s="23"/>
@@ -1931,19 +2031,20 @@
       <c r="I40" s="23"/>
       <c r="J40" s="23"/>
       <c r="K40" s="23"/>
+      <c r="L40" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="10">
     <mergeCell ref="A33:J33"/>
-    <mergeCell ref="A36:K36"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A40:K40"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A39:K39"/>
+    <mergeCell ref="A36:L36"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A40:L40"/>
+    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="A39:L39"/>
     <mergeCell ref="A32:J32"/>
-    <mergeCell ref="A35:K35"/>
-    <mergeCell ref="A38:K38"/>
-    <mergeCell ref="A37:K37"/>
+    <mergeCell ref="A35:L35"/>
+    <mergeCell ref="A38:L38"/>
+    <mergeCell ref="A37:L37"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1960,7 +2061,7 @@
   <sheetData>
     <row r="1" spans="1:26" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="25" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B1" s="23"/>
       <c r="C1" s="23"/>
@@ -1990,7 +2091,7 @@
     </row>
     <row r="2" spans="1:26" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="29" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B2" s="23"/>
       <c r="C2" s="23"/>
@@ -2020,119 +2121,119 @@
     </row>
     <row r="4" spans="1:26" ht="140.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C4" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="E4" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="F4" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="G4" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="G4" s="12" t="s">
+      <c r="H4" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="H4" s="12" t="s">
-        <v>21</v>
-      </c>
       <c r="I4" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="J4" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="J4" s="12" t="s">
+      <c r="K4" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="K4" s="12" t="s">
+      <c r="L4" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="L4" s="12" t="s">
+      <c r="M4" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="M4" s="12" t="s">
+      <c r="N4" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="N4" s="12" t="s">
+      <c r="O4" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="O4" s="12" t="s">
+      <c r="P4" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="P4" s="12" t="s">
+      <c r="Q4" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="Q4" s="12" t="s">
-        <v>31</v>
-      </c>
       <c r="R4" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="S4" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="S4" s="12" t="s">
-        <v>34</v>
-      </c>
       <c r="T4" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="U4" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="U4" s="12" t="s">
+      <c r="V4" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="V4" s="12" t="s">
+      <c r="W4" s="12" t="s">
         <v>38</v>
-      </c>
-      <c r="W4" s="12" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="B5" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="C5" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="D5" s="5" t="s">
         <v>52</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>53</v>
       </c>
       <c r="E5" s="15"/>
       <c r="F5" s="15"/>
       <c r="G5" s="15"/>
       <c r="H5" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K5" s="15"/>
       <c r="L5" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="M5" s="5" t="s">
         <v>52</v>
-      </c>
-      <c r="M5" s="5" t="s">
-        <v>53</v>
       </c>
       <c r="N5" s="15"/>
       <c r="O5" s="15"/>
       <c r="P5" s="15"/>
       <c r="Q5" s="15"/>
       <c r="R5" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="S5" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="T5" s="14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="U5" s="15"/>
       <c r="V5" s="15"/>
@@ -2140,19 +2241,19 @@
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B6" s="15"/>
       <c r="C6" s="15"/>
       <c r="D6" s="14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E6" s="15"/>
       <c r="F6" s="15"/>
       <c r="G6" s="15"/>
       <c r="H6" s="15"/>
       <c r="I6" s="14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J6" s="15"/>
       <c r="K6" s="15"/>
@@ -2163,7 +2264,7 @@
       <c r="P6" s="15"/>
       <c r="Q6" s="15"/>
       <c r="R6" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="S6" s="15"/>
       <c r="T6" s="15"/>
@@ -2173,21 +2274,21 @@
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
       <c r="D7" s="14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F7" s="15"/>
       <c r="G7" s="15"/>
       <c r="H7" s="15"/>
       <c r="I7" s="14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J7" s="15"/>
       <c r="K7" s="15"/>
@@ -2198,7 +2299,7 @@
       <c r="P7" s="15"/>
       <c r="Q7" s="15"/>
       <c r="R7" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="S7" s="15"/>
       <c r="T7" s="15"/>
@@ -2208,13 +2309,13 @@
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B8" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>52</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>53</v>
       </c>
       <c r="D8" s="15"/>
       <c r="E8" s="15"/>
@@ -2222,16 +2323,16 @@
       <c r="G8" s="15"/>
       <c r="H8" s="15"/>
       <c r="I8" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="J8" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="J8" s="5" t="s">
-        <v>53</v>
-      </c>
       <c r="K8" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="L8" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M8" s="15"/>
       <c r="N8" s="15"/>
@@ -2239,7 +2340,7 @@
       <c r="P8" s="15"/>
       <c r="Q8" s="15"/>
       <c r="R8" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="S8" s="15"/>
       <c r="T8" s="15"/>
@@ -2249,13 +2350,13 @@
     </row>
     <row r="9" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D9" s="15"/>
       <c r="E9" s="15"/>
@@ -2266,7 +2367,7 @@
       <c r="J9" s="15"/>
       <c r="K9" s="15"/>
       <c r="L9" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="M9" s="15"/>
       <c r="N9" s="15"/>
@@ -2274,13 +2375,13 @@
       <c r="P9" s="15"/>
       <c r="Q9" s="15"/>
       <c r="R9" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="S9" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="S9" s="5" t="s">
-        <v>53</v>
-      </c>
       <c r="T9" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="U9" s="15"/>
       <c r="V9" s="15"/>
@@ -2288,15 +2389,15 @@
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C10" s="15"/>
       <c r="D10" s="15"/>
       <c r="E10" s="14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F10" s="15"/>
       <c r="G10" s="15"/>
@@ -2311,66 +2412,66 @@
       <c r="P10" s="15"/>
       <c r="Q10" s="15"/>
       <c r="R10" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="S10" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="T10" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="T10" s="5" t="s">
-        <v>53</v>
-      </c>
       <c r="U10" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="V10" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="W10" s="15"/>
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B11" s="14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D11" s="15"/>
       <c r="E11" s="14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F11" s="15"/>
       <c r="G11" s="15"/>
       <c r="H11" s="14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I11" s="14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J11" s="14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="K11" s="14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="L11" s="14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M11" s="14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="N11" s="15"/>
       <c r="O11" s="15"/>
       <c r="P11" s="15"/>
       <c r="Q11" s="15"/>
       <c r="R11" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="S11" s="15"/>
       <c r="T11" s="14" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="U11" s="15"/>
       <c r="V11" s="15"/>
@@ -2378,99 +2479,99 @@
     </row>
     <row r="12" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A12" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="B12" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="B12" s="17" t="s">
-        <v>61</v>
-      </c>
       <c r="C12" s="17" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F12" s="17" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G12" s="17" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H12" s="17" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="I12" s="17" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J12" s="17" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K12" s="17" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="L12" s="17" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="M12" s="17" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="N12" s="15"/>
       <c r="O12" s="17" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="P12" s="15"/>
       <c r="Q12" s="15"/>
       <c r="R12" s="17" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="S12" s="17" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="T12" s="17" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="U12" s="17" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="V12" s="17" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="W12" s="15"/>
     </row>
     <row r="14" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A14" s="18" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="16" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B16" s="20" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B17" s="21" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
